--- a/P4 Pengembangan Kebutuhan Perangkat Lunak/A Elisitasi/A4 Coding/Lembar_Coding_Codebook_1_0_3 (Deni).xlsx
+++ b/P4 Pengembangan Kebutuhan Perangkat Lunak/A Elisitasi/A4 Coding/Lembar_Coding_Codebook_1_0_3 (Deni).xlsx
@@ -6471,8 +6471,8 @@
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8" disablePrompts="0">
-        <x14:dataValidation xr:uid="{40A71BFC-468F-4E02-B34F-0A12AC687FAF}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Kodekan pihak yang secara eksplisit menjadi subjek tata bahasa norma utama pada kolom “Isi”. Jangan menyimpulkan subjek dari judul BAB." showDropDown="0" showErrorMessage="1" showInputMessage="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9" disablePrompts="0">
+        <x14:dataValidation xr:uid="{2C12D510-F333-42A0-A65F-F101EFEB6C2D}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Kodekan pihak yang secara eksplisit menjadi subjek tata bahasa norma utama pada kolom “Isi”. Jangan menyimpulkan subjek dari judul BAB.&#10;Detail lihat Bagian 7.1" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$5:$D$13</xm:f>
           </x14:formula1>
@@ -6481,16 +6481,16 @@
           </x14:formula2>
           <xm:sqref>F3:F86</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{3ADC3A2D-A767-401A-A1D5-A2532BAC3A9F}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Tentukan dengan Uji Implikasi Bagian 6." showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{104A0345-3DA5-4567-9F82-5C0DA5DC4BE0}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Tentukan dengan Uji Implikasi Bagian 6.&#10;Detail lainnya lihat Bagian 7.2" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$16:$D$18</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>"""0"""</xm:f>
           </x14:formula2>
-          <xm:sqref>G2:G86</xm:sqref>
+          <xm:sqref>G2:G20 G22:G86</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{5C8C653D-C2AF-48EA-81F8-5E67A3691DCB}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Pilih satu tema dominan dari pohon keputusan Bagian 7.3. Pemilihan T99 wajib dijelaskan di V12." showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{67B25E2F-91B3-4E9F-8DAE-87B0074D45E4}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Pilih satu tema dominan dari pohon keputusan Bagian 7.3. Pemilihan T99 wajib dijelaskan di V12." showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$21:$D$37</xm:f>
           </x14:formula1>
@@ -6499,7 +6499,7 @@
           </x14:formula2>
           <xm:sqref>H2:H86</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{3FBC73A6-C919-4E5A-B1A8-6965BA15CD3A}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Lihat Bagian 7.4" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{1A755312-4155-4117-85B2-B509B3A4F41F}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Detail lihat Bagian 7.4" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$40:$D$47</xm:f>
           </x14:formula1>
@@ -6508,7 +6508,7 @@
           </x14:formula2>
           <xm:sqref>I2:I86</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{39DADBC4-29FA-40A1-BBDF-CF4432FBF06D}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Tahap siklus data yang terkait dari awal hingga akhir. Lihat Bagian 7.5" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{061700D1-6D39-4AC5-9638-BB214661FD91}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Tahap siklus data yang terkait dari awal hingga akhir.&#10;Detail lihat Bagian 7.5" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$50:$D$57</xm:f>
           </x14:formula1>
@@ -6517,7 +6517,7 @@
           </x14:formula2>
           <xm:sqref>J2:J86</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{572B2A9A-D32D-4F1C-9385-257BECC8E40A}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Kandidat jenis kebutuhan SRS diperiksa berurutan K1 -&gt; K2 -&gt; K3 -&gt; K4 -&gt; K5. Lihat Bagian 7.6" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{6FCE5C41-932D-4A44-8AE0-DBCC91E219D6}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Kandidat jenis kebutuhan SRS diperiksa berurutan K1 -&gt; K2 -&gt; K3 -&gt; K4 -&gt; K5.&#10;Detail lihat Bagian 7.6" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$60:$D$64</xm:f>
           </x14:formula1>
@@ -6526,7 +6526,7 @@
           </x14:formula2>
           <xm:sqref>K2:K86</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{0CD83B93-428A-4E23-B9EE-328C53EDA220}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Tema kedua bila unit memuat dua tema (gunakan kode dari Bagian 7.3). T99 tidak digunakan di sini." promptTitle="Opsional" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{78CEC7C6-A62B-4E2C-98DE-DDE1E79085DB}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Tema kedua bila unit memuat dua tema (gunakan kode dari Bagian 7.3). T99 tidak digunakan di sini." promptTitle="Opsional" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$21:$D$36</xm:f>
           </x14:formula1>
@@ -6535,7 +6535,7 @@
           </x14:formula2>
           <xm:sqref>L2:L86</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{12174727-4766-4F1A-B7C8-45EA0C78E5FC}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Kodekan pihak yang secara eksplisit menjadi subjek tata bahasa norma utama pada kolom “Isi”. Jangan menyimpulkan subjek dari judul BAB." promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{78F1C1B0-1957-4014-9C75-8FD096D53194}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Kodekan pihak yang secara eksplisit menjadi subjek tata bahasa norma utama pada kolom “Isi”. Jangan menyimpulkan subjek dari judul BAB." promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>'Daftar Kode'!$D$5:$D$13</xm:f>
           </x14:formula1>
@@ -6543,6 +6543,15 @@
             <xm:f>"""0"""</xm:f>
           </x14:formula2>
           <xm:sqref>F2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xr:uid="{06824767-2672-45C1-81AB-529C77E37E91}" type="list" allowBlank="1" error="Pilih kode dari daftar (lihat sheet Daftar Kode)." errorStyle="stop" errorTitle="Kode tidak sah" imeMode="noControl" operator="between" prompt="Tentukan dengan Uji Implikasi Bagian 6.&#10;Detail lainnya lihat Bagian 7.2" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+          <x14:formula1>
+            <xm:f>'Daftar Kode'!$D$16:$D$18</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>"""0"""</xm:f>
+          </x14:formula2>
+          <xm:sqref>G21</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
